--- a/data/import/schema/SignatureCases.xlsx
+++ b/data/import/schema/SignatureCases.xlsx
@@ -139,9 +139,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SignatureCases" displayName="SignatureCases" ref="A1:AG7" headerRowCount="1">
-  <autoFilter ref="A1:AG7"/>
-  <tableColumns count="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SignatureCases" displayName="SignatureCases" ref="A1:AH7" headerRowCount="1">
+  <autoFilter ref="A1:AH7"/>
+  <tableColumns count="34">
     <tableColumn id="1" name="DocumentNo"/>
     <tableColumn id="2" name="CustomerName"/>
     <tableColumn id="3" name="CustomerEmail"/>
@@ -166,15 +166,16 @@
     <tableColumn id="22" name="OperatorEmail"/>
     <tableColumn id="23" name="OperatorName"/>
     <tableColumn id="24" name="SignatureImageUrl"/>
-    <tableColumn id="25" name="PdfUrl"/>
-    <tableColumn id="26" name="PdfFileName"/>
-    <tableColumn id="27" name="RegisteredAt"/>
-    <tableColumn id="28" name="SentAt"/>
-    <tableColumn id="29" name="ResendCount"/>
-    <tableColumn id="30" name="ClientRequestId"/>
-    <tableColumn id="31" name="ErrorCode"/>
-    <tableColumn id="32" name="ErrorMessage"/>
-    <tableColumn id="33" name="FlowRunId"/>
+    <tableColumn id="25" name="SignatureImageItemId"/>
+    <tableColumn id="26" name="PdfUrl"/>
+    <tableColumn id="27" name="PdfFileName"/>
+    <tableColumn id="28" name="RegisteredAt"/>
+    <tableColumn id="29" name="SentAt"/>
+    <tableColumn id="30" name="ResendCount"/>
+    <tableColumn id="31" name="ClientRequestId"/>
+    <tableColumn id="32" name="ErrorCode"/>
+    <tableColumn id="33" name="ErrorMessage"/>
+    <tableColumn id="34" name="FlowRunId"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
@@ -469,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG7"/>
+  <dimension ref="A1:AH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -496,15 +497,16 @@
     <col width="19" customWidth="1" min="22" max="22"/>
     <col width="18" customWidth="1" min="23" max="23"/>
     <col width="23" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="17" customWidth="1" min="26" max="26"/>
-    <col width="18" customWidth="1" min="27" max="27"/>
-    <col width="12" customWidth="1" min="28" max="28"/>
-    <col width="17" customWidth="1" min="29" max="29"/>
-    <col width="21" customWidth="1" min="30" max="30"/>
-    <col width="15" customWidth="1" min="31" max="31"/>
-    <col width="18" customWidth="1" min="32" max="32"/>
-    <col width="15" customWidth="1" min="33" max="33"/>
+    <col width="26" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="17" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="17" customWidth="1" min="30" max="30"/>
+    <col width="21" customWidth="1" min="31" max="31"/>
+    <col width="15" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="15" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -630,45 +632,50 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>SignatureImageItemId</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>PdfUrl</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>PdfFileName</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>RegisteredAt</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>SentAt</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>ResendCount</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>ClientRequestId</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>ErrorCode</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>ErrorMessage</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>FlowRunId</t>
         </is>
@@ -791,30 +798,28 @@
           <t>サンプル</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>サンプル</t>
-        </is>
+      <c r="Y2" t="n">
+        <v>1</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
           <t>サンプル</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="n">
-        <v>46023.375</v>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>サンプル</t>
+        </is>
       </c>
       <c r="AB2" s="2" t="n">
         <v>46023.375</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AC2" s="2" t="n">
+        <v>46023.375</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1</v>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>サンプル</t>
-        </is>
-      </c>
       <c r="AE2" t="inlineStr">
         <is>
           <t>サンプル</t>
@@ -822,10 +827,15 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>サンプル本文</t>
+          <t>サンプル</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
+        <is>
+          <t>サンプル本文</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>サンプル</t>
         </is>
@@ -948,30 +958,28 @@
           <t>サンプル</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>サンプル</t>
-        </is>
+      <c r="Y3" t="n">
+        <v>2</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
           <t>サンプル</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="n">
-        <v>46023.375</v>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>サンプル</t>
+        </is>
       </c>
       <c r="AB3" s="2" t="n">
         <v>46023.375</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AC3" s="2" t="n">
+        <v>46023.375</v>
+      </c>
+      <c r="AD3" t="n">
         <v>2</v>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>サンプル</t>
-        </is>
-      </c>
       <c r="AE3" t="inlineStr">
         <is>
           <t>サンプル</t>
@@ -979,10 +987,15 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>サンプル本文</t>
+          <t>サンプル</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
+        <is>
+          <t>サンプル本文</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>サンプル</t>
         </is>
@@ -1105,30 +1118,28 @@
           <t>サンプル</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>サンプル</t>
-        </is>
+      <c r="Y4" t="n">
+        <v>3</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
           <t>サンプル</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="n">
-        <v>46023.375</v>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>サンプル</t>
+        </is>
       </c>
       <c r="AB4" s="2" t="n">
         <v>46023.375</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AC4" s="2" t="n">
+        <v>46023.375</v>
+      </c>
+      <c r="AD4" t="n">
         <v>3</v>
       </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>サンプル</t>
-        </is>
-      </c>
       <c r="AE4" t="inlineStr">
         <is>
           <t>サンプル</t>
@@ -1136,10 +1147,15 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>サンプル本文</t>
+          <t>サンプル</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
+        <is>
+          <t>サンプル本文</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>サンプル</t>
         </is>
@@ -1262,30 +1278,28 @@
           <t>サンプル</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>サンプル</t>
-        </is>
+      <c r="Y5" t="n">
+        <v>4</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
           <t>サンプル</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="n">
-        <v>46023.375</v>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>サンプル</t>
+        </is>
       </c>
       <c r="AB5" s="2" t="n">
         <v>46023.375</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AC5" s="2" t="n">
+        <v>46023.375</v>
+      </c>
+      <c r="AD5" t="n">
         <v>4</v>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>サンプル</t>
-        </is>
-      </c>
       <c r="AE5" t="inlineStr">
         <is>
           <t>サンプル</t>
@@ -1293,10 +1307,15 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>サンプル本文</t>
+          <t>サンプル</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
+        <is>
+          <t>サンプル本文</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>サンプル</t>
         </is>
@@ -1419,30 +1438,28 @@
           <t>サンプル</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>サンプル</t>
-        </is>
+      <c r="Y6" t="n">
+        <v>5</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
           <t>サンプル</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="n">
-        <v>46023.375</v>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>サンプル</t>
+        </is>
       </c>
       <c r="AB6" s="2" t="n">
         <v>46023.375</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AC6" s="2" t="n">
+        <v>46023.375</v>
+      </c>
+      <c r="AD6" t="n">
         <v>5</v>
       </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>サンプル</t>
-        </is>
-      </c>
       <c r="AE6" t="inlineStr">
         <is>
           <t>サンプル</t>
@@ -1450,10 +1467,15 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>サンプル本文</t>
+          <t>サンプル</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
+        <is>
+          <t>サンプル本文</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>サンプル</t>
         </is>
@@ -1576,30 +1598,28 @@
           <t>サンプル</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>サンプル</t>
-        </is>
+      <c r="Y7" t="n">
+        <v>6</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>サンプル</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="n">
-        <v>46023.375</v>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>サンプル</t>
+        </is>
       </c>
       <c r="AB7" s="2" t="n">
         <v>46023.375</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AC7" s="2" t="n">
+        <v>46023.375</v>
+      </c>
+      <c r="AD7" t="n">
         <v>6</v>
       </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>サンプル</t>
-        </is>
-      </c>
       <c r="AE7" t="inlineStr">
         <is>
           <t>サンプル</t>
@@ -1607,10 +1627,15 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>サンプル本文</t>
+          <t>サンプル</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
+        <is>
+          <t>サンプル本文</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
         <is>
           <t>サンプル</t>
         </is>
